--- a/sources/标准汉语会话360句3_语法零基础版.xlsx
+++ b/sources/标准汉语会话360句3_语法零基础版.xlsx
@@ -4,9 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet name="01_语法总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_学生练习版" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_按课索引" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_说明与来源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="进阶练习" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_学生练习版" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_按课索引" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_说明与来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -15,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -26,8 +27,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6656A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B2A1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,6 +287,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -2704,6 +2715,3424 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="62" t="inlineStr">
+        <is>
+          <t>语法编号</t>
+        </is>
+      </c>
+      <c r="B1" s="62" t="inlineStr">
+        <is>
+          <t>课次</t>
+        </is>
+      </c>
+      <c r="C1" s="62" t="inlineStr">
+        <is>
+          <t>题型</t>
+        </is>
+      </c>
+      <c r="D1" s="62" t="inlineStr">
+        <is>
+          <t>题干</t>
+        </is>
+      </c>
+      <c r="E1" s="62" t="inlineStr">
+        <is>
+          <t>选项A</t>
+        </is>
+      </c>
+      <c r="F1" s="62" t="inlineStr">
+        <is>
+          <t>选项B</t>
+        </is>
+      </c>
+      <c r="G1" s="62" t="inlineStr">
+        <is>
+          <t>选项C</t>
+        </is>
+      </c>
+      <c r="H1" s="62" t="inlineStr">
+        <is>
+          <t>选项D</t>
+        </is>
+      </c>
+      <c r="I1" s="62" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="J1" s="62" t="inlineStr">
+        <is>
+          <t>解析（中文）</t>
+        </is>
+      </c>
+      <c r="K1" s="62" t="inlineStr">
+        <is>
+          <t>解析（英文）</t>
+        </is>
+      </c>
+      <c r="L1" s="62" t="inlineStr">
+        <is>
+          <t>题干（英文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.1</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>你们班___多少个学生？</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>在</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>叫</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>问一个地方有多少人或东西，要用“地点＋有”。“是”用来说明已知的东西是什么，这里不行。</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>To ask how many people or things are in a place, use place + 有. 是 only identifies a known thing.</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>How many students are there in your class?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>宿舍旁边有___。</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>每家咖啡厅</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>那家咖啡厅</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>这家咖啡厅</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>一家咖啡厅</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>“有”引出新的、不确定的东西，所以要说“一家”。说已知的“那家”“这家”应该用“是”或“在”。</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>有 introduces something new and not yet known, so use 一家. For a known place (那家/这家) use 是 or 在.</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>There is a café next to the dorm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>食堂对面是足球场。</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>我家附近有一个咖啡厅。</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>我们学校有很多留学生。</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>一家银行是学校旁边。</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>存在句要先说地点，应该说“学校旁边有一家银行”。</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>Put the place first: 学校旁边有一家银行.</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>There are two cafés near our school.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>我们学校附近有两家咖啡厅。</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr"/>
+      <c r="K5" s="14" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>你昨天穿___鞋真好看。</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>地</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>的</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>得</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>了</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>“你昨天穿”说明“鞋”，动词短语和名词中间要用“的”。“了”不能把动词短语和名词连起来。</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>你昨天穿 describes the shoes, so link it to the noun with 的. 了 cannot link a verb phrase to a noun.</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>The shoes you wore yesterday look really nice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>___的那个人是我哥哥。</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>等你在门口</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>在等你门口</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>在门口等你了</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>在门口等你</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>放在“的”前面的动词短语要按正常语序：地点在动词前，后面不加“了”。</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>The verb phrase before 的 keeps normal word order (place before the verb) and takes no 了 at the end.</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>The person waiting for you at the door is my older brother.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>这是我在网上订的票。</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>姐姐做的蛋糕特别好吃。</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>他是教我们汉语老师。</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>你说的那家店在哪儿？</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>动词短语修饰名词要加“的”，应该说“他是教我们汉语的老师”。</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>A verb phrase before a noun needs 的: 他是教我们汉语的老师.</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>360-3.1.2</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>The movie I watched yesterday was very interesting.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>我昨天看的电影很有意思。</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.1</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>我买___票就去找你。</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>过</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>着</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>的</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>了</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>“动词＋了＋宾语，就……”表示一个动作完成以后马上做另一个。“过”表示经历，不能这样用。</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>Verb + 了 + object, 就… means 'after doing one thing, then…'. 过 shows past experience and doesn't fit here.</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>After I buy the ticket, I'll come find you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.1</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>A：你吃了早饭吗？B：我___。</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>还没吃</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>不吃了</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>没吃了</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>没有吃了</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>“了”的否定是“没（有）＋动词”，后面不能再加“了”。“不吃了”是说以后不吃，不是回答过去的事。</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>The negative of verb + 了 is 没 + verb, with no 了. 不吃了 means 'I won't eat any more', not 'I haven't eaten'.</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>Did you eat breakfast? — Not yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.1</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>我昨天看了一个电影。</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>他给我打了一个电话。</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>我昨天没买了票。</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>我们吃了饭就走吧。</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>用“没”否定时去掉“了”，应该说“我昨天没买票”。</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>When you use 没, drop 了: 我昨天没买票.</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.1</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>I bought two tickets.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>我买了两张票。</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.2</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>这两个蛋糕，大___是我的。</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>一点儿</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>了</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>的</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>一个</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>“大的”就是“大的蛋糕”，后面的名词省略了，可以当主语。“大一点儿”只说明大小，不能代替名词。</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>大的 means "the big one" (the noun is left out), so it can be the subject. 大一点儿 only describes size and can't stand for a noun.</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>Of these two cakes, the big one is mine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.2</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>我的鞋是黑色的，___。</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>他是红色的鞋</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>他是红色</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>他红色的</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>他的是红色的</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>这里说的是他的鞋，要用“他的”代替“他的鞋”。“他是红色的鞋”意思变成了“他这个人是红色的鞋”。</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>We mean his shoes, so 他的 replaces 他的鞋. 他是红色的鞋 would say that he himself is red shoes.</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>My shoes are black; his are red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.2</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>我要便宜的。</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>红色的太贵了。</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>这本书不是你，是我。</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>这是老师的，那是我的。</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>说东西属于谁要用“的”字短语，应该说“这本书不是你的，是我的”。</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>To say whose something is, use 的: 这本书不是你的，是我的.</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>360-3.2.2</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>I don't want the red one; I want the black one.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>我不要红色的，我要黑色的。</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.1</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>这家餐厅的菜___便宜又好吃。</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>又</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>也</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>“又……又……”要成对使用，后面有“又好吃”，前面也要用“又”。</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>又…又… comes as a pair; since 又好吃 follows, the first part also needs 又.</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>This restaurant's food is both cheap and tasty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.1</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>这个房间又大又___，我很喜欢。</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>很舒服</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>舒服</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>舒服了</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>真舒服</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>“又”后面直接放形容词，不能再加“很、真”或“了”。</t>
+        </is>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>又 is followed directly by the adjective — no 很, 真 or 了.</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>This room is big and comfortable; I really like it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.1</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>今天又冷又下雨。</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>这个蛋糕又很好看又好吃。</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>这个电影又长又没意思。</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>他的狗又胖又可爱。</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>“又”后面不加“很”，应该说“这个蛋糕又好看又好吃”。</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>Don't put 很 after 又: 这个蛋糕又好看又好吃.</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.1</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>This dog is both small and cute.</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>这只狗又小又可爱。</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.2</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>我想___你一个问题。</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>问</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>说</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>叫</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>听</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>“问”可以带两个宾语：问＋人＋问题。“说、叫、听”都不能说“＋你＋一个问题”。</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>问 can take two objects: 问 + person + question. 说, 叫 and 听 cannot be followed by 你 + 一个问题.</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>I'd like to ask you a question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.2</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>我朋友送___。</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>一本书我</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>我一本书</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>我的一本书</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>对我一本书</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>双宾语句先说人，再说东西：送＋我＋一本书。</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>With two objects, the person comes first, then the thing: 送我一本书.</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>My friend gave me a book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.2</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>王老师教我们唱歌。</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>他给一本书我。</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>妈妈给我两百块钱。</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>我想问你一件事。</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>应该先说人再说东西：他给我一本书。</t>
+        </is>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>Person before thing: 他给我一本书.</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>360-3.3.2</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>My older sister gave me a cake.</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>姐姐送我一个蛋糕。</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.1</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>我叫了你三次，你没听___吗？</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>完</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>见</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>懂</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>“听见”表示声音听到了。叫人名字是问有没有听到，不是问懂不懂。</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>听见 means the sound reached you. When someone calls you, the question is whether you heard, not whether you understood.</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>I called you three times — didn't you hear me?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.1</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>老师说得太快，我___。</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>不听懂</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>没听懂</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>没懂听</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>没听懂了</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>结果补语的否定是“没＋动词＋补语”，不加“了”，也不用“不”。</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>Negate a verb + result with 没, without 了, not with 不.</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>The teacher spoke too fast; I didn't understand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.1</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>你看见我的书了吗？</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>这个问题我答错了。</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>我做作业完了。</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>饭做好了，快来吃吧。</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>结果补语要紧跟在动词后面，宾语放在后面：我做完作业了。</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>The result word goes right after the verb, before the object: 我做完作业了.</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.1</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>I have finished reading this book.</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>这本书我看完了。</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.2</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>___你不舒服，就别去上课了。</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>所以</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>虽然</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>可是</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>要是</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>后面有“就”，前面是一个条件，所以用“要是”。“虽然、可是、所以”不跟“就”这样搭配。</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>就 follows a condition, so the first part needs 要是 ('if'). 虽然, 可是 and 所以 don't pair with 就 like this.</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>If you don't feel well, don't go to class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.2</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>要是明天天气好，___。</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>我们才去打网球</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>我们去就打网球</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>我们就去打了网球</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>我们就去打网球</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>“要是……就……”说还没发生的事，“就”放在主语后、动词前，结果部分不用“了”，也不用“才”。</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>要是…就… is about the future: 就 goes after the subject and before the verb, with no 了 and no 才.</t>
+        </is>
+      </c>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>If the weather is good tomorrow, we'll go play tennis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.2</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>要是你累了，就休息一下吧。</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>要是你不想去，就算了。</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>要是下雨，我们就坐出租车去。</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>要是你喜欢，就我送你。</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>“就”要放在主语后面：要是你喜欢，我就送你。</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>就 goes after the subject: 要是你喜欢，我就送你.</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>360-3.4.2</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>If you like it, I'll buy it for you.</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="14" t="inlineStr"/>
+      <c r="H33" s="14" t="inlineStr"/>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>要是你喜欢，我就给你买。</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14" t="inlineStr"/>
+      <c r="L33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.1</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>我在门口等你，你快出___吧。</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>来</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>去</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>到</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>了</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>说话人在外边门口，动作向着说话人，所以用“出来”。</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>The speaker is outside at the door, and the movement is toward the speaker, so use 出来.</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>I'm waiting for you at the door — hurry and come out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.1</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>你快下来吧，___。</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>我在楼下等你</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>我在楼上等你</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>我在楼上的教室</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>我在你楼上</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>“下来”表示向下、向着说话人，所以说话人在下面，就是在楼下。</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>下来 means moving down toward the speaker, so the speaker must be downstairs.</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>Come on down, I'm waiting for you downstairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.1</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>你什么时候回来？</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>爸爸出去买东西了。</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>外边冷，快进来吧。</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>他回去家了。</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>表示地方的宾语要放在“来/去”前面：他回家去了。</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>A place object goes before 来/去: 他回家去了.</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.1</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>My older brother went back home.</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>哥哥回家去了。</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.2</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>我们先吃饭，___去看电影吧。</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>又</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>“先……再……”说以后要做的两件事的顺序，句末“吧”是在提建议。“又”多用于已经发生的事，“才”强调晚或条件，不用来这样安排以后的事。</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>先…再… orders two actions still to come, and 吧 makes it a suggestion. 又 is mostly for things already done; 才 stresses lateness or a condition and isn't used to plan the next step like this.</t>
+        </is>
+      </c>
+      <c r="L38" s="14" t="inlineStr">
+        <is>
+          <t>Let's eat first, then go see a movie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.2</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>A：咱们去哪儿？B：___，再去商店。</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>去银行先</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>去先银行</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>先银行去</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>先去银行</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>“先”是副词，放在动词前面：先去银行，再去商店。不能像英语那样把“先”放在后面。</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>先 is an adverb and goes before the verb: 先去银行. Don't put it at the end as in English.</t>
+        </is>
+      </c>
+      <c r="L39" s="14" t="inlineStr">
+        <is>
+          <t>Where shall we go? — The bank first, then the store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.2</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>先我们去吃饭，然后去商店。</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>咱们先买票，再进去吧。</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>我先打电话，然后去找你。</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>你先休息一下，再给他打电话吧。</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>“先”是副词，要放在主语后面：我们先去吃饭，然后去商店。</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>先 goes after the subject: 我们先去吃饭，然后去商店.</t>
+        </is>
+      </c>
+      <c r="L40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>360-3.5.2</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>I'll do my homework first, then play tennis.</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>我先做作业，然后去打网球。</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr"/>
+      <c r="L41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.1</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>他___，说得很好。</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>学汉语了两年</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>学了两年汉语</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>学两年了汉语</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>两年学了汉语</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>时间长短放在“动词＋了”后面、名词宾语前面：学了两年汉语。</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>The length of time goes after verb + 了 and before a noun object: 学了两年汉语.</t>
+        </is>
+      </c>
+      <c r="L42" s="14" t="inlineStr">
+        <is>
+          <t>He studied Chinese for two years and speaks it well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.1</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>我在门口等了___。</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>他半个小时</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>他的半个小时</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>半个小时给他</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>半个小时他</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>宾语是人称代词时，放在时间长短前面：等了他半个小时。</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>When the object is a pronoun, it comes before the length of time: 等了他半个小时.</t>
+        </is>
+      </c>
+      <c r="L43" s="14" t="inlineStr">
+        <is>
+          <t>I waited for him at the door for half an hour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.1</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>他打网球了两个小时。</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>我在上海待了一个星期。</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>我学了三个月汉语。</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>我们聊了一会儿天儿。</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>时间长短要放在名词宾语前面：他打了两个小时网球。</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>Put the time before the noun object: 他打了两个小时网球.</t>
+        </is>
+      </c>
+      <c r="L44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.1</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>She studied Chinese in Shanghai for half a year.</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="14" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr"/>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>她在上海学了半年汉语。</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr"/>
+      <c r="K45" s="14" t="inlineStr"/>
+      <c r="L45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.2</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>我是跟朋友一起来___。</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>的</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>呢</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>了</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>地</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>前面有“是”，强调怎么来的，句子后面要用“的”，不用“了”。</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>With 是 stressing how you came, end with 的, not 了.</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
+          <t>I came together with a friend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.2</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>这件衣服是___的。</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>明天去买</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>一会儿去买</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>上个星期买</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>下个星期买</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>“是……的”说已经发生的事，强调时间、地点、方式，不能说将来的事。</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>是…的 is for things that already happened (stressing when/where/how), not for the future.</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr">
+        <is>
+          <t>I bought this piece of clothing last week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.2</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>他是昨天坐飞机来北京了。</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>你是什么时候到的？</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>我是在网上订的票。</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>这个蛋糕是妈妈做的。</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>说过去的时间、方式要用“是……的”，不用“了”：他是昨天坐飞机来北京的。</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>For a past time/manner use 是…的, not 了: 他是昨天坐飞机来北京的.</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>360-3.6.2</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>I came to China last year.</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr"/>
+      <c r="F49" s="14" t="inlineStr"/>
+      <c r="G49" s="14" t="inlineStr"/>
+      <c r="H49" s="14" t="inlineStr"/>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>我是去年来中国的。</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr"/>
+      <c r="K49" s="14" t="inlineStr"/>
+      <c r="L49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.1</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>电影七点开始，他七点半___到。</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>就</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>又</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>七点半比七点晚，说晚了要用“才”。“就”表示早，跟前面的意思不合。</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>7:30 is later than the 7:00 start, so use 才 (late). 就 would mean he was early.</t>
+        </is>
+      </c>
+      <c r="L50" s="14" t="inlineStr">
+        <is>
+          <t>The movie started at seven; he didn't arrive until seven thirty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.1</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>他今天九点才起床，___。</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>起得真早</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>上课又来晚了</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>是第一个到教室的</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>比大家都早</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>“九点才起床”说明起得晚，所以上课来晚了。“起得真早”等都和“才”的意思相反。</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>九点才起床 means he got up late, so he was late for class. The other options mean early, the opposite of 才.</t>
+        </is>
+      </c>
+      <c r="L51" s="14" t="inlineStr">
+        <is>
+          <t>He didn't get up until nine today, and he was late for class again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.1</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>我等了他半天，他十点就来了。</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>八点上课，他七点半就到了。</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>他六点就出门了。</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>我昨天十一点才下班。</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>等了很久才来，说明来得晚，要用“才”：他十点才来。</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>After a long wait, the arrival is late, so use 才: 他十点才来.</t>
+        </is>
+      </c>
+      <c r="L52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.1</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>Class started at eight, but she didn't come until nine.</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr"/>
+      <c r="F53" s="14" t="inlineStr"/>
+      <c r="G53" s="14" t="inlineStr"/>
+      <c r="H53" s="14" t="inlineStr"/>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>八点上课，她九点才来。</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr"/>
+      <c r="K53" s="14" t="inlineStr"/>
+      <c r="L53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.2</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>我找了___，他都不在。</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>两次他</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>两个次他</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>他两次</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>他的两次</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
+          <t>宾语是人称代词时，放在“两次”前面：找了他两次。</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="inlineStr">
+        <is>
+          <t>When the object is a pronoun, it goes before the count: 找了他两次.</t>
+        </is>
+      </c>
+      <c r="L54" s="14" t="inlineStr">
+        <is>
+          <t>I looked for him twice, but he wasn't in either time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.2</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>上个星期我打了___。</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>三次的网球</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>三次了网球</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>三次网球</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>网球了三次</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>名词宾语放在“三次”后面：打了三次网球。</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>A noun object goes after the count: 打了三次网球.</t>
+        </is>
+      </c>
+      <c r="L55" s="14" t="inlineStr">
+        <is>
+          <t>Last week I played tennis three times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.2</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>这个电影我看过两遍。</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>我们见过一次面。</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>我两次看过这个电影。</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>请你再说一遍。</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>“两次”要放在动词后面：我看过两次这个电影。</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>The count goes after the verb: 我看过两次这个电影.</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>360-3.7.2</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>I went to the library three times last week.</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr"/>
+      <c r="F57" s="14" t="inlineStr"/>
+      <c r="G57" s="14" t="inlineStr"/>
+      <c r="H57" s="14" t="inlineStr"/>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>我上个星期去了三次图书馆。</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="inlineStr"/>
+      <c r="K57" s="14" t="inlineStr"/>
+      <c r="L57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.1</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>图书馆里有___人。</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>三十个多</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>多三十个</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>三十多个</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>三多十个</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="inlineStr">
+        <is>
+          <t>整十后面加“多”，再加量词：三十多个。</t>
+        </is>
+      </c>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>多 comes right after a round number and before the measure word: 三十多个.</t>
+        </is>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
+        <is>
+          <t>There are over thirty people in the library.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.1</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>A：你们班有多少学生？B：___。</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>十七个八吧</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>十七八多个吧</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>十八七个吧</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>十七八个吧</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>相邻的两个数连着说，小的在前，后面不再加“多”：十七八个。</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>Say two neighbouring numbers together, smaller first, without 多: 十七八个.</t>
+        </is>
+      </c>
+      <c r="L59" s="14" t="inlineStr">
+        <is>
+          <t>How many students are in your class? — About seventeen or eighteen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.1</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>这个包两百块多。</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>我买了两三斤苹果。</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>这儿有五六个人。</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>我等了二十多分钟。</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>“多”要放在量词前面：这个包两百多块。</t>
+        </is>
+      </c>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>多 goes before the measure word: 这个包两百多块.</t>
+        </is>
+      </c>
+      <c r="L60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.1</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>There are about seven or eight people in the room.</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr"/>
+      <c r="F61" s="14" t="inlineStr"/>
+      <c r="G61" s="14" t="inlineStr"/>
+      <c r="H61" s="14" t="inlineStr"/>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>房间里有七八个人。</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr"/>
+      <c r="K61" s="14" t="inlineStr"/>
+      <c r="L61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.2</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>火车___开了，你快上去吧。</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>正在</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>一直</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>快要</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>在</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
+        <is>
+          <t>“快要……了”表示马上就要发生，所以要快上车。“正在、在”表示动作在进行，不和句尾“了”这样用。</t>
+        </is>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>快要…了 means something is about to happen, so you must hurry. 正在/在 show an ongoing action and don't pair with 了 here.</t>
+        </is>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>The train is about to leave; hurry and get on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.2</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>电影快开始了，___。</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>我们已经出来了</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>咱们快进去吧</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>咱们看了一半了</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>咱们刚看完了</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>“快开始了”表示电影还没开始，马上要开始，所以应该赶快进去。</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>快开始了 means the movie hasn't started yet but will very soon, so it's time to go in.</t>
+        </is>
+      </c>
+      <c r="L63" s="14" t="inlineStr">
+        <is>
+          <t>The movie is about to start; let's hurry in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.2</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>快下雨了，我们回去吧。</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>要上课了，快进教室吧。</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>我快要到家了。</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>我们快要考试。</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr">
+        <is>
+          <t>“快要”后面句子末尾要有“了”：我们快要考试了。</t>
+        </is>
+      </c>
+      <c r="K64" s="14" t="inlineStr">
+        <is>
+          <t>快要 needs 了 at the end: 我们快要考试了.</t>
+        </is>
+      </c>
+      <c r="L64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>360-3.8.2</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>It's going to rain soon.</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr"/>
+      <c r="F65" s="14" t="inlineStr"/>
+      <c r="G65" s="14" t="inlineStr"/>
+      <c r="H65" s="14" t="inlineStr"/>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>快要下雨了。</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="inlineStr"/>
+      <c r="K65" s="14" t="inlineStr"/>
+      <c r="L65" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4181,7 +7610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4416,13 +7845,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -4573,6 +8002,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>进阶练习（网站，2026-10）</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>「进阶练习」表是为网站新写的进阶题：每个语法点辨析选择、完成句子、找错各 1 道（点选作答，带中英文解析；入门册另附题干英文），难度按本册水平控制，经出题、正确性+难度审核、终审三轮把关。网站上它们替换了 01 表「练习1–3」中的填空/选择/排序等题；翻译题保留，其中答案与例句完全相同的，在本表换成了新句子（题型=翻译）。01 表原有练习未改动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
